--- a/output/pdf_financials_xlsx/TAUR.xlsx
+++ b/output/pdf_financials_xlsx/TAUR.xlsx
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.4148</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.528209</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.264938</v>
       </c>
     </row>
     <row r="93">
@@ -3067,7 +3067,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -3259,7 +3263,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>0.4148</v>
       </c>

--- a/output/pdf_financials_xlsx/TAUR.xlsx
+++ b/output/pdf_financials_xlsx/TAUR.xlsx
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.004987</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.005507</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.476164</v>
+        <v>-1.481151</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.972766</v>
+        <v>-0.9782729999999999</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-2.246216</v>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.476164</v>
+        <v>-1.481151</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.972766</v>
+        <v>-0.9782729999999999</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-2.246216</v>
@@ -988,13 +988,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.623509</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.010062</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000198</v>
       </c>
     </row>
     <row r="35">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.623509</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.010062</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000198</v>
       </c>
     </row>
     <row r="37">
@@ -1212,13 +1212,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.627982</v>
+        <v>0.004473</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.015921</v>
+        <v>0.005859</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.005937</v>
+        <v>0.005739</v>
       </c>
     </row>
     <row r="49">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">

--- a/output/pdf_financials_xlsx/TAUR.xlsx
+++ b/output/pdf_financials_xlsx/TAUR.xlsx
@@ -3986,7 +3986,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E43" s="5" t="n">
         <v>-0.077</v>
       </c>
@@ -5152,7 +5156,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E81" s="5" t="n">
         <v>0.077</v>
       </c>
